--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1154,6 +1154,3422 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120488008</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90351</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>698724</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6359394</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120488021</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>698637</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6359418</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120488006</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87350</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Toppvaxskivling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>698626</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6359214</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120488859</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90351</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>698721</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6359349</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120488031</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>698838</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6359286</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120488007</v>
+      </c>
+      <c r="B11" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>424</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>698707</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6359402</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120488037</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698908</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6359365</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120488011</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>698830</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6359312</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120488860</v>
+      </c>
+      <c r="B14" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>698714</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6359371</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120488027</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698713</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6359339</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120488009</v>
+      </c>
+      <c r="B16" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>698659</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6359219</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120488034</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>698947</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6359433</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120488020</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90021</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>698715</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6359369</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120488033</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>698936</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6359413</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120488005</v>
+      </c>
+      <c r="B20" t="n">
+        <v>86465</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>698724</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6359394</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120488022</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>698664</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6359395</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120488039</v>
+      </c>
+      <c r="B22" t="n">
+        <v>86338</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>249248</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blek bananspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius citrinoolivaceus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>698734</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6359381</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120488025</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>698750</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6359373</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120488035</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>698930</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6359382</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120488038</v>
+      </c>
+      <c r="B25" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>698637</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6359418</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120488858</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102848</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>698660</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6359396</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Åsa Kestrup</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120488029</v>
+      </c>
+      <c r="B27" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>698767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6359225</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120488041</v>
+      </c>
+      <c r="B28" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>698610</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6359329</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120488013</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>698930</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6359382</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120488010</v>
+      </c>
+      <c r="B30" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>698735</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6359401</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120488032</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>698841</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6359308</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120488030</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>698818</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6359256</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120488019</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>698685</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6359276</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120488024</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>698772</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6359379</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120488018</v>
+      </c>
+      <c r="B35" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>698638</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6359265</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120488012</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>698936</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6359413</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120488026</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Öst Ansarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>698721</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6359398</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120488008</v>
+        <v>120488037</v>
       </c>
       <c r="B6" t="n">
-        <v>90351</v>
+        <v>100194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698724</v>
+        <v>698908</v>
       </c>
       <c r="R6" t="n">
-        <v>6359394</v>
+        <v>6359365</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120488021</v>
+        <v>120488034</v>
       </c>
       <c r="B7" t="n">
         <v>100194</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698637</v>
+        <v>698947</v>
       </c>
       <c r="R7" t="n">
-        <v>6359418</v>
+        <v>6359433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120488006</v>
+        <v>120488008</v>
       </c>
       <c r="B8" t="n">
-        <v>87350</v>
+        <v>90351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4379</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698626</v>
+        <v>698724</v>
       </c>
       <c r="R8" t="n">
-        <v>6359214</v>
+        <v>6359394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1455,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1478,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120488859</v>
+        <v>120488018</v>
       </c>
       <c r="B9" t="n">
-        <v>90351</v>
+        <v>86373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,50 +1489,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>248956</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698721</v>
+        <v>698638</v>
       </c>
       <c r="R9" t="n">
-        <v>6359349</v>
+        <v>6359265</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,12 +1567,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1593,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120488031</v>
+        <v>120488038</v>
       </c>
       <c r="B10" t="n">
-        <v>100194</v>
+        <v>86282</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>3712</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1633,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698838</v>
+        <v>698637</v>
       </c>
       <c r="R10" t="n">
-        <v>6359286</v>
+        <v>6359418</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120488007</v>
+        <v>120488022</v>
       </c>
       <c r="B11" t="n">
-        <v>86302</v>
+        <v>100194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,25 +1701,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>424</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698707</v>
+        <v>698664</v>
       </c>
       <c r="R11" t="n">
-        <v>6359402</v>
+        <v>6359395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120488037</v>
+        <v>120488019</v>
       </c>
       <c r="B12" t="n">
-        <v>100194</v>
+        <v>86373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>248956</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698908</v>
+        <v>698685</v>
       </c>
       <c r="R12" t="n">
-        <v>6359365</v>
+        <v>6359276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120488011</v>
+        <v>120488010</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>86449</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,25 +1913,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698830</v>
+        <v>698735</v>
       </c>
       <c r="R13" t="n">
-        <v>6359312</v>
+        <v>6359401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120488860</v>
+        <v>120488029</v>
       </c>
       <c r="B14" t="n">
-        <v>86449</v>
+        <v>100194</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,50 +2019,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698714</v>
+        <v>698767</v>
       </c>
       <c r="R14" t="n">
-        <v>6359371</v>
+        <v>6359225</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,12 +2097,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2132,7 +2113,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120488027</v>
+        <v>120488032</v>
       </c>
       <c r="B15" t="n">
         <v>100194</v>
@@ -2172,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698713</v>
+        <v>698841</v>
       </c>
       <c r="R15" t="n">
-        <v>6359339</v>
+        <v>6359308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488009</v>
+        <v>120488041</v>
       </c>
       <c r="B16" t="n">
-        <v>86449</v>
+        <v>86414</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,25 +2231,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698659</v>
+        <v>698610</v>
       </c>
       <c r="R16" t="n">
-        <v>6359219</v>
+        <v>6359329</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2325,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120488034</v>
+        <v>120488035</v>
       </c>
       <c r="B17" t="n">
         <v>100194</v>
@@ -2384,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698947</v>
+        <v>698930</v>
       </c>
       <c r="R17" t="n">
-        <v>6359433</v>
+        <v>6359382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120488020</v>
+        <v>120488860</v>
       </c>
       <c r="B18" t="n">
-        <v>90021</v>
+        <v>86449</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2462,41 +2443,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4188</v>
+        <v>6003295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698715</v>
+        <v>698714</v>
       </c>
       <c r="R18" t="n">
-        <v>6359369</v>
+        <v>6359371</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2540,12 +2530,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2556,7 +2546,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120488033</v>
+        <v>120488027</v>
       </c>
       <c r="B19" t="n">
         <v>100194</v>
@@ -2596,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698936</v>
+        <v>698713</v>
       </c>
       <c r="R19" t="n">
-        <v>6359413</v>
+        <v>6359339</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2662,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120488005</v>
+        <v>120488006</v>
       </c>
       <c r="B20" t="n">
-        <v>86465</v>
+        <v>87350</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,25 +2664,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>248947</v>
+        <v>4379</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Toppvaxskivling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698724</v>
+        <v>698626</v>
       </c>
       <c r="R20" t="n">
-        <v>6359394</v>
+        <v>6359214</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,6 +2736,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2768,7 +2759,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120488022</v>
+        <v>120488031</v>
       </c>
       <c r="B21" t="n">
         <v>100194</v>
@@ -2808,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698664</v>
+        <v>698838</v>
       </c>
       <c r="R21" t="n">
-        <v>6359395</v>
+        <v>6359286</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2874,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120488039</v>
+        <v>120488009</v>
       </c>
       <c r="B22" t="n">
-        <v>86338</v>
+        <v>86449</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2886,20 +2877,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>249248</v>
+        <v>6003295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blek bananspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius citrinoolivaceus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2914,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698734</v>
+        <v>698659</v>
       </c>
       <c r="R22" t="n">
-        <v>6359381</v>
+        <v>6359219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,12 +2935,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,7 +2971,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120488025</v>
+        <v>120488024</v>
       </c>
       <c r="B23" t="n">
         <v>100194</v>
@@ -3020,10 +3011,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698750</v>
+        <v>698772</v>
       </c>
       <c r="R23" t="n">
-        <v>6359373</v>
+        <v>6359379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3086,7 +3077,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120488035</v>
+        <v>120488033</v>
       </c>
       <c r="B24" t="n">
         <v>100194</v>
@@ -3126,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698930</v>
+        <v>698936</v>
       </c>
       <c r="R24" t="n">
-        <v>6359382</v>
+        <v>6359413</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,10 +3183,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120488038</v>
+        <v>120488026</v>
       </c>
       <c r="B25" t="n">
-        <v>86282</v>
+        <v>100194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3208,21 +3199,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3712</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698637</v>
+        <v>698721</v>
       </c>
       <c r="R25" t="n">
-        <v>6359418</v>
+        <v>6359398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3298,10 +3289,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120488858</v>
+        <v>120488030</v>
       </c>
       <c r="B26" t="n">
-        <v>102848</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,41 +3305,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698660</v>
+        <v>698818</v>
       </c>
       <c r="R26" t="n">
-        <v>6359396</v>
+        <v>6359256</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3386,19 +3373,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3409,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120488029</v>
+        <v>120488007</v>
       </c>
       <c r="B27" t="n">
-        <v>100194</v>
+        <v>86302</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3421,25 +3407,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>424</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3449,10 +3435,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698767</v>
+        <v>698707</v>
       </c>
       <c r="R27" t="n">
-        <v>6359225</v>
+        <v>6359402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3515,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120488041</v>
+        <v>120488021</v>
       </c>
       <c r="B28" t="n">
-        <v>86414</v>
+        <v>100194</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3531,21 +3517,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3674</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3555,10 +3541,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698610</v>
+        <v>698637</v>
       </c>
       <c r="R28" t="n">
-        <v>6359329</v>
+        <v>6359418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3621,7 +3607,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120488013</v>
+        <v>120488011</v>
       </c>
       <c r="B29" t="n">
         <v>57689</v>
@@ -3661,10 +3647,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698930</v>
+        <v>698830</v>
       </c>
       <c r="R29" t="n">
-        <v>6359382</v>
+        <v>6359312</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3727,10 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120488010</v>
+        <v>120488005</v>
       </c>
       <c r="B30" t="n">
-        <v>86449</v>
+        <v>86465</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3739,25 +3725,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3767,10 +3753,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>698735</v>
+        <v>698724</v>
       </c>
       <c r="R30" t="n">
-        <v>6359401</v>
+        <v>6359394</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,7 +3819,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120488032</v>
+        <v>120488025</v>
       </c>
       <c r="B31" t="n">
         <v>100194</v>
@@ -3873,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698841</v>
+        <v>698750</v>
       </c>
       <c r="R31" t="n">
-        <v>6359308</v>
+        <v>6359373</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3939,10 +3925,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120488030</v>
+        <v>120488013</v>
       </c>
       <c r="B32" t="n">
-        <v>100194</v>
+        <v>57689</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3955,21 +3941,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3979,10 +3965,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698818</v>
+        <v>698930</v>
       </c>
       <c r="R32" t="n">
-        <v>6359256</v>
+        <v>6359382</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4045,10 +4031,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120488019</v>
+        <v>120488012</v>
       </c>
       <c r="B33" t="n">
-        <v>86373</v>
+        <v>57689</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4057,25 +4043,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>248956</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>698685</v>
+        <v>698936</v>
       </c>
       <c r="R33" t="n">
-        <v>6359276</v>
+        <v>6359413</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4151,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120488024</v>
+        <v>120488859</v>
       </c>
       <c r="B34" t="n">
-        <v>100194</v>
+        <v>90351</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4167,37 +4153,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>698772</v>
+        <v>698721</v>
       </c>
       <c r="R34" t="n">
-        <v>6359379</v>
+        <v>6359349</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4241,12 +4236,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4257,10 +4252,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120488018</v>
+        <v>120488020</v>
       </c>
       <c r="B35" t="n">
-        <v>86373</v>
+        <v>90021</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4269,25 +4264,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>248956</v>
+        <v>4188</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4297,10 +4292,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>698638</v>
+        <v>698715</v>
       </c>
       <c r="R35" t="n">
-        <v>6359265</v>
+        <v>6359369</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,10 +4358,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120488012</v>
+        <v>120488858</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>102848</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4379,37 +4374,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>222002</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>698936</v>
+        <v>698660</v>
       </c>
       <c r="R36" t="n">
-        <v>6359413</v>
+        <v>6359396</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4447,127 +4446,22 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>120488026</v>
-      </c>
-      <c r="B37" t="n">
-        <v>100194</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Öst Ansarve, Gtl</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>698721</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6359398</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Fröjel</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120488037</v>
+        <v>120488034</v>
       </c>
       <c r="B6" t="n">
         <v>100194</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698908</v>
+        <v>698947</v>
       </c>
       <c r="R6" t="n">
-        <v>6359365</v>
+        <v>6359433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120488034</v>
+        <v>120488005</v>
       </c>
       <c r="B7" t="n">
-        <v>100194</v>
+        <v>86465</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,25 +1277,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>248947</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698947</v>
+        <v>698724</v>
       </c>
       <c r="R7" t="n">
-        <v>6359433</v>
+        <v>6359394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120488008</v>
+        <v>120488031</v>
       </c>
       <c r="B8" t="n">
-        <v>90351</v>
+        <v>100194</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698724</v>
+        <v>698838</v>
       </c>
       <c r="R8" t="n">
-        <v>6359394</v>
+        <v>6359286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120488018</v>
+        <v>120488012</v>
       </c>
       <c r="B9" t="n">
-        <v>86373</v>
+        <v>57689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,25 +1489,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>248956</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698638</v>
+        <v>698936</v>
       </c>
       <c r="R9" t="n">
-        <v>6359265</v>
+        <v>6359413</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120488038</v>
+        <v>120488006</v>
       </c>
       <c r="B10" t="n">
-        <v>86282</v>
+        <v>87350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3712</v>
+        <v>4379</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Toppvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698637</v>
+        <v>698626</v>
       </c>
       <c r="R10" t="n">
-        <v>6359418</v>
+        <v>6359214</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,6 +1667,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1689,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120488022</v>
+        <v>120488019</v>
       </c>
       <c r="B11" t="n">
-        <v>100194</v>
+        <v>86373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,25 +1702,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>248956</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698664</v>
+        <v>698685</v>
       </c>
       <c r="R11" t="n">
-        <v>6359395</v>
+        <v>6359276</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120488019</v>
+        <v>120488860</v>
       </c>
       <c r="B12" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,41 +1808,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698685</v>
+        <v>698714</v>
       </c>
       <c r="R12" t="n">
-        <v>6359276</v>
+        <v>6359371</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,12 +1895,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2007,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120488029</v>
+        <v>120488033</v>
       </c>
       <c r="B14" t="n">
         <v>100194</v>
@@ -2047,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698767</v>
+        <v>698936</v>
       </c>
       <c r="R14" t="n">
-        <v>6359225</v>
+        <v>6359413</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2123,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120488032</v>
+        <v>120488021</v>
       </c>
       <c r="B15" t="n">
         <v>100194</v>
@@ -2153,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698841</v>
+        <v>698637</v>
       </c>
       <c r="R15" t="n">
-        <v>6359308</v>
+        <v>6359418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488041</v>
+        <v>120488013</v>
       </c>
       <c r="B16" t="n">
-        <v>86414</v>
+        <v>57689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,21 +2245,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3674</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2259,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698610</v>
+        <v>698930</v>
       </c>
       <c r="R16" t="n">
-        <v>6359329</v>
+        <v>6359382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2335,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120488035</v>
+        <v>120488037</v>
       </c>
       <c r="B17" t="n">
         <v>100194</v>
@@ -2365,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698930</v>
+        <v>698908</v>
       </c>
       <c r="R17" t="n">
-        <v>6359382</v>
+        <v>6359365</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2431,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120488860</v>
+        <v>120488030</v>
       </c>
       <c r="B18" t="n">
-        <v>86449</v>
+        <v>100194</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2443,50 +2453,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698714</v>
+        <v>698818</v>
       </c>
       <c r="R18" t="n">
-        <v>6359371</v>
+        <v>6359256</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,12 +2531,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2546,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120488027</v>
+        <v>120488020</v>
       </c>
       <c r="B19" t="n">
-        <v>100194</v>
+        <v>90021</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2562,21 +2563,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>4188</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2586,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698713</v>
+        <v>698715</v>
       </c>
       <c r="R19" t="n">
-        <v>6359339</v>
+        <v>6359369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120488006</v>
+        <v>120488025</v>
       </c>
       <c r="B20" t="n">
-        <v>87350</v>
+        <v>100194</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2668,21 +2669,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4379</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2692,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698626</v>
+        <v>698750</v>
       </c>
       <c r="R20" t="n">
-        <v>6359214</v>
+        <v>6359373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,7 +2737,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120488031</v>
+        <v>120488024</v>
       </c>
       <c r="B21" t="n">
         <v>100194</v>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698838</v>
+        <v>698772</v>
       </c>
       <c r="R21" t="n">
-        <v>6359286</v>
+        <v>6359379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120488009</v>
+        <v>120488007</v>
       </c>
       <c r="B22" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2877,25 +2877,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698659</v>
+        <v>698707</v>
       </c>
       <c r="R22" t="n">
-        <v>6359219</v>
+        <v>6359402</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120488024</v>
+        <v>120488018</v>
       </c>
       <c r="B23" t="n">
-        <v>100194</v>
+        <v>86373</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2983,25 +2983,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>248956</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698772</v>
+        <v>698638</v>
       </c>
       <c r="R23" t="n">
-        <v>6359379</v>
+        <v>6359265</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120488033</v>
+        <v>120488859</v>
       </c>
       <c r="B24" t="n">
-        <v>100194</v>
+        <v>90351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,37 +3093,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698936</v>
+        <v>698721</v>
       </c>
       <c r="R24" t="n">
-        <v>6359413</v>
+        <v>6359349</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3167,12 +3176,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3183,10 +3192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120488026</v>
+        <v>120488008</v>
       </c>
       <c r="B25" t="n">
-        <v>100194</v>
+        <v>90351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3199,21 +3208,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3223,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698721</v>
+        <v>698724</v>
       </c>
       <c r="R25" t="n">
-        <v>6359398</v>
+        <v>6359394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3289,7 +3298,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120488030</v>
+        <v>120488022</v>
       </c>
       <c r="B26" t="n">
         <v>100194</v>
@@ -3329,10 +3338,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698818</v>
+        <v>698664</v>
       </c>
       <c r="R26" t="n">
-        <v>6359256</v>
+        <v>6359395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3395,10 +3404,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120488007</v>
+        <v>120488011</v>
       </c>
       <c r="B27" t="n">
-        <v>86302</v>
+        <v>57689</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3407,25 +3416,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>424</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3435,10 +3444,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698707</v>
+        <v>698830</v>
       </c>
       <c r="R27" t="n">
-        <v>6359402</v>
+        <v>6359312</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3501,10 +3510,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120488021</v>
+        <v>120488009</v>
       </c>
       <c r="B28" t="n">
-        <v>100194</v>
+        <v>86449</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3513,25 +3522,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3541,10 +3550,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698637</v>
+        <v>698659</v>
       </c>
       <c r="R28" t="n">
-        <v>6359418</v>
+        <v>6359219</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120488011</v>
+        <v>120488038</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>86282</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3623,21 +3632,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>3712</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3647,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698830</v>
+        <v>698637</v>
       </c>
       <c r="R29" t="n">
-        <v>6359312</v>
+        <v>6359418</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3713,10 +3722,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120488005</v>
+        <v>120488027</v>
       </c>
       <c r="B30" t="n">
-        <v>86465</v>
+        <v>100194</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3725,25 +3734,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>248947</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3753,10 +3762,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>698724</v>
+        <v>698713</v>
       </c>
       <c r="R30" t="n">
-        <v>6359394</v>
+        <v>6359339</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3819,7 +3828,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120488025</v>
+        <v>120488029</v>
       </c>
       <c r="B31" t="n">
         <v>100194</v>
@@ -3859,10 +3868,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698750</v>
+        <v>698767</v>
       </c>
       <c r="R31" t="n">
-        <v>6359373</v>
+        <v>6359225</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3925,10 +3934,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120488013</v>
+        <v>120488858</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>102848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3941,37 +3950,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>222002</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>698930</v>
+        <v>698660</v>
       </c>
       <c r="R32" t="n">
-        <v>6359382</v>
+        <v>6359396</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4009,18 +4022,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4031,10 +4045,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120488012</v>
+        <v>120488041</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>86414</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4047,21 +4061,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4071,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>698936</v>
+        <v>698610</v>
       </c>
       <c r="R33" t="n">
-        <v>6359413</v>
+        <v>6359329</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4137,10 +4151,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120488859</v>
+        <v>120488032</v>
       </c>
       <c r="B34" t="n">
-        <v>90351</v>
+        <v>100194</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4153,46 +4167,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>698721</v>
+        <v>698841</v>
       </c>
       <c r="R34" t="n">
-        <v>6359349</v>
+        <v>6359308</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4236,12 +4241,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4252,10 +4257,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120488020</v>
+        <v>120488036</v>
       </c>
       <c r="B35" t="n">
-        <v>90021</v>
+        <v>100194</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4268,21 +4273,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4188</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4292,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>698715</v>
+        <v>698930</v>
       </c>
       <c r="R35" t="n">
-        <v>6359369</v>
+        <v>6359382</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4358,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120488858</v>
+        <v>120488026</v>
       </c>
       <c r="B36" t="n">
-        <v>102848</v>
+        <v>100194</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4374,41 +4379,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>698660</v>
+        <v>698721</v>
       </c>
       <c r="R36" t="n">
-        <v>6359396</v>
+        <v>6359398</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4446,19 +4447,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120488034</v>
+        <v>120488041</v>
       </c>
       <c r="B6" t="n">
-        <v>100194</v>
+        <v>86414</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,21 +1175,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698947</v>
+        <v>698610</v>
       </c>
       <c r="R6" t="n">
-        <v>6359433</v>
+        <v>6359329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120488031</v>
+        <v>120488026</v>
       </c>
       <c r="B8" t="n">
         <v>100194</v>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698838</v>
+        <v>698721</v>
       </c>
       <c r="R8" t="n">
-        <v>6359286</v>
+        <v>6359398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120488012</v>
+        <v>120488008</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>90351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698936</v>
+        <v>698724</v>
       </c>
       <c r="R9" t="n">
-        <v>6359413</v>
+        <v>6359394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120488006</v>
+        <v>120488027</v>
       </c>
       <c r="B10" t="n">
-        <v>87350</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4379</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698626</v>
+        <v>698713</v>
       </c>
       <c r="R10" t="n">
-        <v>6359214</v>
+        <v>6359339</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1667,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1690,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120488019</v>
+        <v>120488010</v>
       </c>
       <c r="B11" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,25 +1701,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698685</v>
+        <v>698735</v>
       </c>
       <c r="R11" t="n">
-        <v>6359276</v>
+        <v>6359401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120488860</v>
+        <v>120488009</v>
       </c>
       <c r="B12" t="n">
         <v>86449</v>
@@ -1829,29 +1828,20 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698714</v>
+        <v>698659</v>
       </c>
       <c r="R12" t="n">
-        <v>6359371</v>
+        <v>6359219</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,12 +1885,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1911,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120488010</v>
+        <v>120488018</v>
       </c>
       <c r="B13" t="n">
-        <v>86449</v>
+        <v>86373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,25 +1913,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698735</v>
+        <v>698638</v>
       </c>
       <c r="R13" t="n">
-        <v>6359401</v>
+        <v>6359265</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120488033</v>
+        <v>120488036</v>
       </c>
       <c r="B14" t="n">
         <v>100194</v>
@@ -2057,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698936</v>
+        <v>698930</v>
       </c>
       <c r="R14" t="n">
-        <v>6359413</v>
+        <v>6359382</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,7 +2113,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120488021</v>
+        <v>120488031</v>
       </c>
       <c r="B15" t="n">
         <v>100194</v>
@@ -2163,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698637</v>
+        <v>698838</v>
       </c>
       <c r="R15" t="n">
-        <v>6359418</v>
+        <v>6359286</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120488013</v>
+        <v>120488034</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>100194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2269,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698930</v>
+        <v>698947</v>
       </c>
       <c r="R16" t="n">
-        <v>6359382</v>
+        <v>6359433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120488037</v>
+        <v>120488013</v>
       </c>
       <c r="B17" t="n">
-        <v>100194</v>
+        <v>57689</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,21 +2341,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698908</v>
+        <v>698930</v>
       </c>
       <c r="R17" t="n">
-        <v>6359365</v>
+        <v>6359382</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,7 +2431,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120488030</v>
+        <v>120488032</v>
       </c>
       <c r="B18" t="n">
         <v>100194</v>
@@ -2481,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698818</v>
+        <v>698841</v>
       </c>
       <c r="R18" t="n">
-        <v>6359256</v>
+        <v>6359308</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,10 +2537,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120488020</v>
+        <v>120488038</v>
       </c>
       <c r="B19" t="n">
-        <v>90021</v>
+        <v>86282</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2563,21 +2553,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4188</v>
+        <v>3712</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2587,10 +2577,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698715</v>
+        <v>698637</v>
       </c>
       <c r="R19" t="n">
-        <v>6359369</v>
+        <v>6359418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,10 +2643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120488025</v>
+        <v>120488006</v>
       </c>
       <c r="B20" t="n">
-        <v>100194</v>
+        <v>87350</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,21 +2659,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>4379</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Toppvaxskivling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2693,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698750</v>
+        <v>698626</v>
       </c>
       <c r="R20" t="n">
-        <v>6359373</v>
+        <v>6359214</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2737,6 +2727,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2759,10 +2750,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120488024</v>
+        <v>120488859</v>
       </c>
       <c r="B21" t="n">
-        <v>100194</v>
+        <v>90351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2775,37 +2766,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698772</v>
+        <v>698721</v>
       </c>
       <c r="R21" t="n">
-        <v>6359379</v>
+        <v>6359349</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,12 +2849,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120488007</v>
+        <v>120488020</v>
       </c>
       <c r="B22" t="n">
-        <v>86302</v>
+        <v>90021</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2877,25 +2877,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>424</v>
+        <v>4188</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698707</v>
+        <v>698715</v>
       </c>
       <c r="R22" t="n">
-        <v>6359402</v>
+        <v>6359369</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120488018</v>
+        <v>120488012</v>
       </c>
       <c r="B23" t="n">
-        <v>86373</v>
+        <v>57689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2983,25 +2983,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>248956</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698638</v>
+        <v>698936</v>
       </c>
       <c r="R23" t="n">
-        <v>6359265</v>
+        <v>6359413</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120488859</v>
+        <v>120488025</v>
       </c>
       <c r="B24" t="n">
-        <v>90351</v>
+        <v>100194</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,46 +3093,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698721</v>
+        <v>698750</v>
       </c>
       <c r="R24" t="n">
-        <v>6359349</v>
+        <v>6359373</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3176,12 +3167,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3192,10 +3183,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120488008</v>
+        <v>120488007</v>
       </c>
       <c r="B25" t="n">
-        <v>90351</v>
+        <v>86302</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,25 +3195,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3223,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698724</v>
+        <v>698707</v>
       </c>
       <c r="R25" t="n">
-        <v>6359394</v>
+        <v>6359402</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3298,10 +3289,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120488022</v>
+        <v>120488019</v>
       </c>
       <c r="B26" t="n">
-        <v>100194</v>
+        <v>86373</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3310,25 +3301,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>248956</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3338,10 +3329,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698664</v>
+        <v>698685</v>
       </c>
       <c r="R26" t="n">
-        <v>6359395</v>
+        <v>6359276</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3404,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120488011</v>
+        <v>120488021</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>100194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3420,21 +3411,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3444,10 +3435,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698830</v>
+        <v>698637</v>
       </c>
       <c r="R27" t="n">
-        <v>6359312</v>
+        <v>6359418</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3510,7 +3501,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120488009</v>
+        <v>120488860</v>
       </c>
       <c r="B28" t="n">
         <v>86449</v>
@@ -3543,20 +3534,29 @@
           <t>M.M.Moser</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698659</v>
+        <v>698714</v>
       </c>
       <c r="R28" t="n">
-        <v>6359219</v>
+        <v>6359371</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3600,12 +3600,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120488038</v>
+        <v>120488011</v>
       </c>
       <c r="B29" t="n">
-        <v>86282</v>
+        <v>57689</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3632,21 +3632,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3712</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>698637</v>
+        <v>698830</v>
       </c>
       <c r="R29" t="n">
-        <v>6359418</v>
+        <v>6359312</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3722,7 +3722,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120488027</v>
+        <v>120488037</v>
       </c>
       <c r="B30" t="n">
         <v>100194</v>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>698713</v>
+        <v>698908</v>
       </c>
       <c r="R30" t="n">
-        <v>6359339</v>
+        <v>6359365</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120488041</v>
+        <v>120488022</v>
       </c>
       <c r="B33" t="n">
-        <v>86414</v>
+        <v>100194</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3674</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>698610</v>
+        <v>698664</v>
       </c>
       <c r="R33" t="n">
-        <v>6359329</v>
+        <v>6359395</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120488032</v>
+        <v>120488033</v>
       </c>
       <c r="B34" t="n">
         <v>100194</v>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>698841</v>
+        <v>698936</v>
       </c>
       <c r="R34" t="n">
-        <v>6359308</v>
+        <v>6359413</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120488036</v>
+        <v>120488024</v>
       </c>
       <c r="B35" t="n">
         <v>100194</v>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>698930</v>
+        <v>698772</v>
       </c>
       <c r="R35" t="n">
-        <v>6359382</v>
+        <v>6359379</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120488026</v>
+        <v>120488030</v>
       </c>
       <c r="B36" t="n">
         <v>100194</v>
@@ -4403,10 +4403,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>698721</v>
+        <v>698818</v>
       </c>
       <c r="R36" t="n">
-        <v>6359398</v>
+        <v>6359256</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -2643,10 +2643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120488006</v>
+        <v>120488012</v>
       </c>
       <c r="B20" t="n">
-        <v>87350</v>
+        <v>57689</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2659,21 +2659,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4379</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698626</v>
+        <v>698936</v>
       </c>
       <c r="R20" t="n">
-        <v>6359214</v>
+        <v>6359413</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,7 +2727,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2750,10 +2749,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120488859</v>
+        <v>120488025</v>
       </c>
       <c r="B21" t="n">
-        <v>90351</v>
+        <v>100194</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,46 +2765,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Öst Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698721</v>
+        <v>698750</v>
       </c>
       <c r="R21" t="n">
-        <v>6359349</v>
+        <v>6359373</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,12 +2839,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2865,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120488020</v>
+        <v>120488006</v>
       </c>
       <c r="B22" t="n">
-        <v>90021</v>
+        <v>87350</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2881,21 +2871,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4188</v>
+        <v>4379</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Toppvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2905,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698715</v>
+        <v>698626</v>
       </c>
       <c r="R22" t="n">
-        <v>6359369</v>
+        <v>6359214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2949,6 +2939,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2971,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120488012</v>
+        <v>120488859</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>90351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2987,37 +2978,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>3215</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öst Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698936</v>
+        <v>698721</v>
       </c>
       <c r="R23" t="n">
-        <v>6359413</v>
+        <v>6359349</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3077,10 +3077,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120488025</v>
+        <v>120488020</v>
       </c>
       <c r="B24" t="n">
-        <v>100194</v>
+        <v>90021</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>4188</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698750</v>
+        <v>698715</v>
       </c>
       <c r="R24" t="n">
-        <v>6359373</v>
+        <v>6359369</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120488024</v>
+        <v>120488030</v>
       </c>
       <c r="B35" t="n">
         <v>100194</v>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>698772</v>
+        <v>698818</v>
       </c>
       <c r="R35" t="n">
-        <v>6359379</v>
+        <v>6359256</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120488030</v>
+        <v>120488024</v>
       </c>
       <c r="B36" t="n">
         <v>100194</v>
@@ -4403,10 +4403,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>698818</v>
+        <v>698772</v>
       </c>
       <c r="R36" t="n">
-        <v>6359256</v>
+        <v>6359379</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698641.4078486057</v>
+        <v>698641</v>
       </c>
       <c r="R2" t="n">
-        <v>6359204.966922268</v>
+        <v>6359205</v>
       </c>
       <c r="S2" t="n">
         <v>71</v>
@@ -748,19 +743,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698641.4078486057</v>
+        <v>698641</v>
       </c>
       <c r="R3" t="n">
-        <v>6359204.966922268</v>
+        <v>6359205</v>
       </c>
       <c r="S3" t="n">
         <v>71</v>
@@ -869,19 +849,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,12 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>96247</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698641.4078486057</v>
+        <v>698641</v>
       </c>
       <c r="R4" t="n">
-        <v>6359204.966922268</v>
+        <v>6359205</v>
       </c>
       <c r="S4" t="n">
         <v>71</v>
@@ -990,19 +955,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,12 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>95990</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698641.4078486057</v>
+        <v>698641</v>
       </c>
       <c r="R5" t="n">
-        <v>6359204.966922268</v>
+        <v>6359205</v>
       </c>
       <c r="S5" t="n">
         <v>71</v>
@@ -1111,19 +1061,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99254</v>
+        <v>99260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105519</v>
+        <v>105528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98491</v>
+        <v>98497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>98111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105528</v>
+        <v>105540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98497</v>
+        <v>98500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98111</v>
+        <v>98114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105540</v>
+        <v>105549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98500</v>
+        <v>98503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98114</v>
+        <v>98116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105549</v>
+        <v>105552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98116</v>
+        <v>98117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105552</v>
+        <v>105580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98117</v>
+        <v>98144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105580</v>
+        <v>105586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98531</v>
+        <v>98537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98144</v>
+        <v>98150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105586</v>
+        <v>105593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98537</v>
+        <v>98544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98150</v>
+        <v>98157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99309</v>
+        <v>99313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105593</v>
+        <v>105597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98544</v>
+        <v>98548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98157</v>
+        <v>98161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99313</v>
+        <v>99320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105597</v>
+        <v>105604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98548</v>
+        <v>98555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98161</v>
+        <v>98168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105607</v>
+        <v>105612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98558</v>
+        <v>98563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98171</v>
+        <v>98176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34100-2024 artfynd.xlsx
+++ b/artfynd/A 34100-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106375716</v>
       </c>
       <c r="B2" t="n">
-        <v>99328</v>
+        <v>99336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106375714</v>
       </c>
       <c r="B3" t="n">
-        <v>105612</v>
+        <v>105620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>106375713</v>
       </c>
       <c r="B4" t="n">
-        <v>98563</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>106375717</v>
       </c>
       <c r="B5" t="n">
-        <v>98176</v>
+        <v>98184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
